--- a/tests/fixtures/13_hr_attendance/data-export-control.xlsx
+++ b/tests/fixtures/13_hr_attendance/data-export-control.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -560,130 +560,131 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>att.month</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>att.working</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>att.absent</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>att.reason</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Sick leave</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E7" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Personal leave</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n">
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>3</v>
       </c>
     </row>
